--- a/sony lens.xlsx
+++ b/sony lens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\personl\camera\lenshistory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C77FF9-6317-4E2E-94D8-3F4D657639C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8244C07-3EC5-4DC6-9D8C-29D055063A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prime_定焦鏡" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3127" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="1106">
   <si>
     <t>廠牌</t>
   </si>
@@ -4051,7 +4051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T131"/>
+  <dimension ref="A1:U234"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:20" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="T128" s="6"/>
     </row>
-    <row r="129" spans="1:20" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>58</v>
       </c>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="T129" s="6"/>
     </row>
-    <row r="130" spans="1:20" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>79</v>
       </c>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="T130" s="6"/>
     </row>
-    <row r="131" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -11135,6 +11135,5199 @@
       <c r="R131" s="6"/>
       <c r="S131" s="6"/>
       <c r="T131" s="6"/>
+    </row>
+    <row r="132" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="133" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P133" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q133" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R133" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S133" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U133" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J134" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K134" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L134" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M134" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N134" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O134" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P134" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q134" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R134" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S134" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T134" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U134" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B135" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="G135" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="J135" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="K135" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="L135" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="M135" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="N135" s="1"/>
+      <c r="O135" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P135" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q135" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R135" s="11">
+        <v>44013</v>
+      </c>
+      <c r="S135" s="10">
+        <v>2020</v>
+      </c>
+      <c r="T135" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="U135" s="45">
+        <v>85980</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B136" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="J136" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="K136" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="L136" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="M136" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="N136" s="1"/>
+      <c r="O136" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P136" s="1"/>
+      <c r="Q136" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R136" s="11">
+        <v>42856</v>
+      </c>
+      <c r="S136" s="10">
+        <v>2017</v>
+      </c>
+      <c r="T136" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="U136" s="45">
+        <v>51980</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B137" s="1"/>
+      <c r="C137" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="G137" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I137" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="J137" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="K137" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="L137" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M137" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="N137" s="1"/>
+      <c r="O137" s="1"/>
+      <c r="P137" s="1"/>
+      <c r="Q137" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R137" s="11">
+        <v>45778</v>
+      </c>
+      <c r="S137" s="10">
+        <v>2025</v>
+      </c>
+      <c r="T137" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="U137" s="45">
+        <v>42990</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="G138" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I138" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="J138" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="K138" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="L138" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="M138" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="N138" s="1"/>
+      <c r="O138" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P138" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q138" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R138" s="11">
+        <v>43709</v>
+      </c>
+      <c r="S138" s="10">
+        <v>2019</v>
+      </c>
+      <c r="T138" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="U138" s="45">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B139" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="G139" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="J139" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="K139" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="L139" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="M139" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="N139" s="1"/>
+      <c r="O139" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P139" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q139" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R139" s="11">
+        <v>45383</v>
+      </c>
+      <c r="S139" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T139" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="U139" s="45">
+        <v>38980</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="G140" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="J140" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K140" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="L140" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="M140" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N140" s="1"/>
+      <c r="O140" s="1"/>
+      <c r="P140" s="1"/>
+      <c r="Q140" s="1"/>
+      <c r="R140" s="11">
+        <v>44713</v>
+      </c>
+      <c r="S140" s="10">
+        <v>2022</v>
+      </c>
+      <c r="T140" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="U140" s="45">
+        <v>27800</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="G141" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="J141" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="K141" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="L141" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M141" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N141" s="1"/>
+      <c r="O141" s="1"/>
+      <c r="P141" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q141" s="1"/>
+      <c r="R141" s="11">
+        <v>45839</v>
+      </c>
+      <c r="S141" s="10">
+        <v>2025</v>
+      </c>
+      <c r="T141" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="U141" s="45">
+        <v>29900</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B142" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="G142" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I142" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="J142" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="K142" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="L142" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="M142" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N142" s="1"/>
+      <c r="O142" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P142" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q142" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R142" s="11">
+        <v>42856</v>
+      </c>
+      <c r="S142" s="10">
+        <v>2017</v>
+      </c>
+      <c r="T142" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="U142" s="45">
+        <v>67980</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B143" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="G143" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I143" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="J143" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K143" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="L143" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="M143" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="N143" s="1"/>
+      <c r="O143" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P143" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q143" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R143" s="11">
+        <v>45139</v>
+      </c>
+      <c r="S143" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T143" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="U143" s="45">
+        <v>69980</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B144" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I144" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="J144" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="K144" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="L144" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="M144" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N144" s="1"/>
+      <c r="O144" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
+      <c r="R144" s="11">
+        <v>43709</v>
+      </c>
+      <c r="S144" s="10">
+        <v>2019</v>
+      </c>
+      <c r="T144" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="U144" s="45">
+        <v>179980</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B145" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="G145" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I145" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="J145" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="K145" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="L145" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="M145" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N145" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O145" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P145" s="1"/>
+      <c r="Q145" s="1"/>
+      <c r="R145" s="11">
+        <v>41760</v>
+      </c>
+      <c r="S145" s="10">
+        <v>2014</v>
+      </c>
+      <c r="T145" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="U145" s="45">
+        <v>36980</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B146" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E146" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I146" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="J146" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="K146" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="L146" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M146" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="N146" s="1"/>
+      <c r="O146" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P146" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q146" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R146" s="11">
+        <v>44621</v>
+      </c>
+      <c r="S146" s="10">
+        <v>2022</v>
+      </c>
+      <c r="T146" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="U146" s="45">
+        <v>36980</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B147" s="1"/>
+      <c r="C147" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="G147" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="J147" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="K147" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="L147" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M147" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N147" s="1"/>
+      <c r="O147" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P147" s="1"/>
+      <c r="Q147" s="1"/>
+      <c r="R147" s="11">
+        <v>43497</v>
+      </c>
+      <c r="S147" s="10">
+        <v>2019</v>
+      </c>
+      <c r="T147" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="U147" s="45">
+        <v>29200</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B148" s="1"/>
+      <c r="C148" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E148" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="F148" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I148" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="J148" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="K148" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="L148" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M148" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="N148" s="1"/>
+      <c r="O148" s="1"/>
+      <c r="P148" s="1"/>
+      <c r="Q148" s="1"/>
+      <c r="R148" s="11">
+        <v>45170</v>
+      </c>
+      <c r="S148" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T148" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="U148" s="45">
+        <v>24800</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" ht="130.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B149" s="1"/>
+      <c r="C149" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="G149" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I149" s="17" t="s">
+        <v>728</v>
+      </c>
+      <c r="J149" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="K149" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="L149" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="M149" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="N149" s="1"/>
+      <c r="O149" s="1"/>
+      <c r="P149" s="1"/>
+      <c r="Q149" s="1"/>
+      <c r="R149" s="11">
+        <v>44774</v>
+      </c>
+      <c r="S149" s="10">
+        <v>2022</v>
+      </c>
+      <c r="T149" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="U149" s="45">
+        <v>24800</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B150" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E150" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="F150" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="J150" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="K150" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="L150" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="M150" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="N150" s="1"/>
+      <c r="O150" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P150" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q150" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R150" s="11">
+        <v>44927</v>
+      </c>
+      <c r="S150" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T150" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="U150" s="45">
+        <v>33980</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B151" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="F151" s="17" t="s">
+        <v>737</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="J151" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K151" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="L151" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="M151" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="N151" s="1"/>
+      <c r="O151" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P151" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q151" s="1"/>
+      <c r="R151" s="11">
+        <v>45901</v>
+      </c>
+      <c r="S151" s="10">
+        <v>2025</v>
+      </c>
+      <c r="T151" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="U151" s="45">
+        <v>29800</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B152" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E152" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="G152" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H152" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="J152" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="K152" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="L152" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M152" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N152" s="1"/>
+      <c r="O152" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P152" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q152" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R152" s="11">
+        <v>45323</v>
+      </c>
+      <c r="S152" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T152" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="U152" s="45">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B153" s="1"/>
+      <c r="C153" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G153" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="J153" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="K153" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="L153" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="M153" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="N153" s="1"/>
+      <c r="O153" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P153" s="1"/>
+      <c r="Q153" s="1"/>
+      <c r="R153" s="11">
+        <v>44470</v>
+      </c>
+      <c r="S153" s="10">
+        <v>2021</v>
+      </c>
+      <c r="T153" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="U153" s="45">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G154" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="J154" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K154" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="L154" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M154" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="N154" s="1"/>
+      <c r="O154" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P154" s="1"/>
+      <c r="Q154" s="1"/>
+      <c r="R154" s="11">
+        <v>43770</v>
+      </c>
+      <c r="S154" s="10">
+        <v>2019</v>
+      </c>
+      <c r="T154" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="U154" s="45">
+        <v>33900</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B155" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G155" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I155" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="J155" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K155" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="L155" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="M155" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="N155" s="1"/>
+      <c r="O155" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P155" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q155" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R155" s="11">
+        <v>45413</v>
+      </c>
+      <c r="S155" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T155" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="U155" s="45">
+        <v>39880</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B156" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E156" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G156" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I156" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="J156" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="K156" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="L156" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="M156" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N156" s="1"/>
+      <c r="O156" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P156" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q156" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R156" s="11">
+        <v>42430</v>
+      </c>
+      <c r="S156" s="10">
+        <v>2016</v>
+      </c>
+      <c r="T156" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="U156" s="45">
+        <v>61980</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B157" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G157" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H157" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I157" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="J157" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K157" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="L157" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="M157" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="N157" s="1"/>
+      <c r="O157" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P157" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q157" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R157" s="11">
+        <v>44652</v>
+      </c>
+      <c r="S157" s="10">
+        <v>2022</v>
+      </c>
+      <c r="T157" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="U157" s="45">
+        <v>55980</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B158" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="J158" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="K158" s="17" t="s">
+        <v>774</v>
+      </c>
+      <c r="L158" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="M158" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="N158" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O158" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P158" s="1"/>
+      <c r="Q158" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R158" s="11">
+        <v>41640</v>
+      </c>
+      <c r="S158" s="10">
+        <v>2014</v>
+      </c>
+      <c r="T158" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="U158" s="45">
+        <v>28980</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B159" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="F159" s="17" t="s">
+        <v>779</v>
+      </c>
+      <c r="G159" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I159" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="J159" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="K159" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="L159" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="M159" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="N159" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O159" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P159" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q159" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R159" s="11">
+        <v>43009</v>
+      </c>
+      <c r="S159" s="10">
+        <v>2017</v>
+      </c>
+      <c r="T159" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="U159" s="45">
+        <v>41980</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="F160" s="17" t="s">
+        <v>737</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="J160" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="K160" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="L160" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="M160" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="N160" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O160" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P160" s="1"/>
+      <c r="Q160" s="1"/>
+      <c r="R160" s="11">
+        <v>42064</v>
+      </c>
+      <c r="S160" s="10">
+        <v>2015</v>
+      </c>
+      <c r="T160" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="U160" s="45">
+        <v>29980</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B161" s="1"/>
+      <c r="C161" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="F161" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="G161" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I161" s="9" t="s">
+        <v>792</v>
+      </c>
+      <c r="J161" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="K161" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="L161" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="M161" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="N161" s="1"/>
+      <c r="O161" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P161" s="1"/>
+      <c r="Q161" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R161" s="11">
+        <v>45931</v>
+      </c>
+      <c r="S161" s="10">
+        <v>2025</v>
+      </c>
+      <c r="T161" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="U161" s="1"/>
+    </row>
+    <row r="162" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="G162" s="33" t="s">
+        <v>800</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I162" s="9" t="s">
+        <v>801</v>
+      </c>
+      <c r="J162" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K162" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="L162" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="M162" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="N162" s="1"/>
+      <c r="O162" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P162" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q162" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R162" s="11">
+        <v>45444</v>
+      </c>
+      <c r="S162" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T162" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="U162" s="45">
+        <v>45880</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B163" s="1"/>
+      <c r="C163" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="G163" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="I163" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="J163" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="K163" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="L163" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="M163" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="N163" s="1"/>
+      <c r="O163" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P163" s="1"/>
+      <c r="Q163" s="1"/>
+      <c r="R163" s="11">
+        <v>44075</v>
+      </c>
+      <c r="S163" s="10">
+        <v>2020</v>
+      </c>
+      <c r="T163" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="U163" s="45">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B164" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="G164" s="33" t="s">
+        <v>811</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="J164" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="K164" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="L164" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="M164" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="N164" s="1"/>
+      <c r="O164" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P164" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q164" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R164" s="11">
+        <v>45597</v>
+      </c>
+      <c r="S164" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T164" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="U164" s="45">
+        <v>92980</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B165" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E165" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="G165" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H165" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="J165" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="K165" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="L165" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M165" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N165" s="1"/>
+      <c r="O165" s="1"/>
+      <c r="P165" s="1"/>
+      <c r="Q165" s="1"/>
+      <c r="R165" s="11">
+        <v>44228</v>
+      </c>
+      <c r="S165" s="10">
+        <v>2021</v>
+      </c>
+      <c r="T165" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="U165" s="45">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B166" s="1"/>
+      <c r="C166" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E166" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>810</v>
+      </c>
+      <c r="G166" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="H166" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="I166" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J166" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="K166" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="L166" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="M166" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N166" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O166" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P166" s="1"/>
+      <c r="Q166" s="1"/>
+      <c r="R166" s="11">
+        <v>41548</v>
+      </c>
+      <c r="S166" s="10">
+        <v>2013</v>
+      </c>
+      <c r="T166" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="U166" s="45">
+        <v>14980</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B167" s="1"/>
+      <c r="C167" s="8" t="s">
+        <v>822</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="G167" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H167" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="J167" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="K167" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="L167" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M167" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="N167" s="1"/>
+      <c r="O167" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P167" s="1"/>
+      <c r="Q167" s="1"/>
+      <c r="R167" s="11">
+        <v>43191</v>
+      </c>
+      <c r="S167" s="10">
+        <v>2018</v>
+      </c>
+      <c r="T167" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="U167" s="45">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B168" s="1"/>
+      <c r="C168" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="G168" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H168" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="J168" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="K168" s="9" t="s">
+        <v>830</v>
+      </c>
+      <c r="L168" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M168" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="N168" s="1"/>
+      <c r="O168" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P168" s="1"/>
+      <c r="Q168" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R168" s="11">
+        <v>44470</v>
+      </c>
+      <c r="S168" s="10">
+        <v>2021</v>
+      </c>
+      <c r="T168" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="U168" s="45">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E169" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="F169" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="G169" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H169" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J169" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K169" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="L169" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="M169" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="N169" s="1"/>
+      <c r="O169" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P169" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q169" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R169" s="11">
+        <v>45536</v>
+      </c>
+      <c r="S169" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T169" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="U169" s="45">
+        <v>52600</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B170" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E170" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="F170" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="G170" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H170" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="J170" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="K170" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="L170" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="M170" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="N170" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O170" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P170" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q170" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R170" s="11">
+        <v>41883</v>
+      </c>
+      <c r="S170" s="10">
+        <v>2014</v>
+      </c>
+      <c r="T170" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="U170" s="45">
+        <v>74980</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B171" s="1"/>
+      <c r="C171" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="F171" s="17" t="s">
+        <v>845</v>
+      </c>
+      <c r="G171" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="H171" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="J171" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="K171" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="L171" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M171" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="N171" s="1"/>
+      <c r="O171" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P171" s="1"/>
+      <c r="Q171" s="1"/>
+      <c r="R171" s="11">
+        <v>43983</v>
+      </c>
+      <c r="S171" s="10">
+        <v>2020</v>
+      </c>
+      <c r="T171" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="U171" s="45">
+        <v>20800</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B172" s="1"/>
+      <c r="C172" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="F172" s="17" t="s">
+        <v>850</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>851</v>
+      </c>
+      <c r="H172" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J172" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="K172" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="L172" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="M172" s="17" t="s">
+        <v>853</v>
+      </c>
+      <c r="N172" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O172" s="1"/>
+      <c r="P172" s="1"/>
+      <c r="Q172" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R172" s="11">
+        <v>45474</v>
+      </c>
+      <c r="S172" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T172" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="U172" s="45">
+        <v>29800</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B173" s="1"/>
+      <c r="C173" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G173" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H173" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="J173" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="K173" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="L173" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="M173" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N173" s="1"/>
+      <c r="O173" s="1"/>
+      <c r="P173" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q173" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R173" s="11">
+        <v>46054</v>
+      </c>
+      <c r="S173" s="10">
+        <v>2026</v>
+      </c>
+      <c r="T173" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="U173" s="45">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B174" s="1"/>
+      <c r="C174" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="F174" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="G174" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="H174" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="J174" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="K174" s="9" t="s">
+        <v>863</v>
+      </c>
+      <c r="L174" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="M174" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N174" s="1"/>
+      <c r="O174" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P174" s="1"/>
+      <c r="Q174" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R174" s="11">
+        <v>45017</v>
+      </c>
+      <c r="S174" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T174" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="U174" s="45">
+        <v>34600</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B175" s="1"/>
+      <c r="C175" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="F175" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="G175" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="H175" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="J175" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="K175" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="L175" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="M175" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N175" s="1"/>
+      <c r="O175" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P175" s="1"/>
+      <c r="Q175" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R175" s="11">
+        <v>44470</v>
+      </c>
+      <c r="S175" s="10">
+        <v>2021</v>
+      </c>
+      <c r="T175" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="U175" s="45">
+        <v>45800</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B176" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="F176" s="17" t="s">
+        <v>871</v>
+      </c>
+      <c r="G176" s="33" t="s">
+        <v>811</v>
+      </c>
+      <c r="H176" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="J176" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="K176" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="L176" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="M176" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="N176" s="1"/>
+      <c r="O176" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P176" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q176" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R176" s="11">
+        <v>45748</v>
+      </c>
+      <c r="S176" s="10">
+        <v>2025</v>
+      </c>
+      <c r="T176" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="U176" s="45">
+        <v>116980</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B177" s="1"/>
+      <c r="C177" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="F177" s="17" t="s">
+        <v>877</v>
+      </c>
+      <c r="G177" s="10" t="s">
+        <v>878</v>
+      </c>
+      <c r="H177" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="J177" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K177" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="L177" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="M177" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="N177" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O177" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P177" s="1"/>
+      <c r="Q177" s="1"/>
+      <c r="R177" s="11">
+        <v>45444</v>
+      </c>
+      <c r="S177" s="10">
+        <v>2024</v>
+      </c>
+      <c r="T177" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="U177" s="45">
+        <v>26800</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B178" s="1"/>
+      <c r="C178" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="F178" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>878</v>
+      </c>
+      <c r="H178" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="J178" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="K178" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="L178" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="M178" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="N178" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O178" s="1"/>
+      <c r="P178" s="1"/>
+      <c r="Q178" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R178" s="11">
+        <v>44774</v>
+      </c>
+      <c r="S178" s="10">
+        <v>2022</v>
+      </c>
+      <c r="T178" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="U178" s="45">
+        <v>40800</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B179" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="F179" s="17" t="s">
+        <v>737</v>
+      </c>
+      <c r="G179" s="10" t="s">
+        <v>878</v>
+      </c>
+      <c r="H179" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="J179" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="K179" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="L179" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="M179" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N179" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O179" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P179" s="1"/>
+      <c r="Q179" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R179" s="11">
+        <v>44927</v>
+      </c>
+      <c r="S179" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T179" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="U179" s="45">
+        <v>64900</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B180" s="1"/>
+      <c r="C180" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="G180" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H180" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="J180" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="K180" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="L180" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="M180" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="N180" s="1"/>
+      <c r="O180" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P180" s="1"/>
+      <c r="Q180" s="1"/>
+      <c r="R180" s="11">
+        <v>43739</v>
+      </c>
+      <c r="S180" s="10">
+        <v>2019</v>
+      </c>
+      <c r="T180" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="U180" s="45">
+        <v>35800</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B181" s="1"/>
+      <c r="C181" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="G181" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H181" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I181" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="J181" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K181" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="L181" s="9" t="s">
+        <v>802</v>
+      </c>
+      <c r="M181" s="17" t="s">
+        <v>902</v>
+      </c>
+      <c r="N181" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O181" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P181" s="1"/>
+      <c r="Q181" s="1"/>
+      <c r="R181" s="11">
+        <v>45170</v>
+      </c>
+      <c r="S181" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T181" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="U181" s="45">
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G182" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H182" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I182" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="J182" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="K182" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="L182" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="M182" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N182" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O182" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P182" s="1"/>
+      <c r="Q182" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R182" s="11">
+        <v>45231</v>
+      </c>
+      <c r="S182" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T182" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="U182" s="45">
+        <v>49800</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B183" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G183" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H183" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="J183" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="K183" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="L183" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="M183" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="N183" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O183" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P183" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q183" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R183" s="11">
+        <v>42401</v>
+      </c>
+      <c r="S183" s="10">
+        <v>2016</v>
+      </c>
+      <c r="T183" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="U183" s="45">
+        <v>76980</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B184" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G184" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="H184" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="J184" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="K184" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="L184" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="M184" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N184" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O184" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P184" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q184" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R184" s="11">
+        <v>44531</v>
+      </c>
+      <c r="S184" s="10">
+        <v>2021</v>
+      </c>
+      <c r="T184" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="U184" s="45">
+        <v>76980</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B185" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="F185" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G185" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H185" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="J185" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K185" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="L185" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="M185" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="N185" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O185" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P185" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q185" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R185" s="11">
+        <v>42552</v>
+      </c>
+      <c r="S185" s="10">
+        <v>2016</v>
+      </c>
+      <c r="T185" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="U185" s="45">
+        <v>42980</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B186" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H186" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I186" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="J186" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K186" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="L186" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="M186" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="N186" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O186" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P186" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q186" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R186" s="11">
+        <v>45108</v>
+      </c>
+      <c r="S186" s="10">
+        <v>2023</v>
+      </c>
+      <c r="T186" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="U186" s="45">
+        <v>47980</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B187" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="F187" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="G187" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="H187" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="J187" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="K187" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="L187" s="9" t="s">
+        <v>929</v>
+      </c>
+      <c r="M187" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="N187" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O187" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P187" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q187" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R187" s="11">
+        <v>42430</v>
+      </c>
+      <c r="S187" s="10">
+        <v>2016</v>
+      </c>
+      <c r="T187" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="U187" s="45">
+        <v>35980</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B188" s="1"/>
+      <c r="C188" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="F188" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="G188" s="10" t="s">
+        <v>878</v>
+      </c>
+      <c r="H188" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I188" s="9" t="s">
+        <v>931</v>
+      </c>
+      <c r="J188" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="K188" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="L188" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="M188" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="N188" s="1"/>
+      <c r="O188" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P188" s="1"/>
+      <c r="Q188" s="1"/>
+      <c r="R188" s="11">
+        <v>44075</v>
+      </c>
+      <c r="S188" s="10">
+        <v>2020</v>
+      </c>
+      <c r="T188" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="U188" s="45">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B189" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="F189" s="17" t="s">
+        <v>936</v>
+      </c>
+      <c r="G189" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="H189" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I189" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="J189" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="K189" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="L189" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="M189" s="17" t="s">
+        <v>941</v>
+      </c>
+      <c r="N189" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O189" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P189" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q189" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R189" s="11">
+        <v>42826</v>
+      </c>
+      <c r="S189" s="10">
+        <v>2017</v>
+      </c>
+      <c r="T189" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="U189" s="45">
+        <v>75980</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B190" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="F190" s="17" t="s">
+        <v>936</v>
+      </c>
+      <c r="G190" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="H190" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="J190" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="K190" s="9" t="s">
+        <v>946</v>
+      </c>
+      <c r="L190" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="M190" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N190" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O190" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P190" s="1"/>
+      <c r="Q190" s="1"/>
+      <c r="R190" s="11">
+        <v>43983</v>
+      </c>
+      <c r="S190" s="10">
+        <v>2020</v>
+      </c>
+      <c r="T190" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="U190" s="45">
+        <v>27800</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B191" s="1"/>
+      <c r="C191" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="F191" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="G191" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="H191" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I191" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="J191" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="K191" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="L191" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="M191" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="N191" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O191" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P191" s="1"/>
+      <c r="Q191" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R191" s="11">
+        <v>44287</v>
+      </c>
+      <c r="S191" s="10">
+        <v>2021</v>
+      </c>
+      <c r="T191" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="U191" s="45">
+        <v>36800</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B192" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="F192" s="17" t="s">
+        <v>936</v>
+      </c>
+      <c r="G192" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="H192" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>957</v>
+      </c>
+      <c r="J192" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="K192" s="9" t="s">
+        <v>959</v>
+      </c>
+      <c r="L192" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="M192" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="N192" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O192" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P192" s="1"/>
+      <c r="Q192" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R192" s="11">
+        <v>44409</v>
+      </c>
+      <c r="S192" s="10">
+        <v>2021</v>
+      </c>
+      <c r="T192" s="9" t="s">
+        <v>961</v>
+      </c>
+      <c r="U192" s="45">
+        <v>39900</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B193" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>963</v>
+      </c>
+      <c r="F193" s="17" t="s">
+        <v>871</v>
+      </c>
+      <c r="G193" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="H193" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="I193" s="9" t="s">
+        <v>964</v>
+      </c>
+      <c r="J193" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="K193" s="9" t="s">
+        <v>965</v>
+      </c>
+      <c r="L193" s="9" t="s">
+        <v>966</v>
+      </c>
+      <c r="M193" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="N193" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O193" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P193" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q193" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R193" s="11">
+        <v>43617</v>
+      </c>
+      <c r="S193" s="10">
+        <v>2019</v>
+      </c>
+      <c r="T193" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="U193" s="45">
+        <v>57980</v>
+      </c>
+    </row>
+    <row r="194" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>968</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="G194" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="H194" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="J194" s="9" t="s">
+        <v>970</v>
+      </c>
+      <c r="K194" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="L194" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="M194" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="N194" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O194" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P194" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q194" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R194" s="11">
+        <v>45689</v>
+      </c>
+      <c r="S194" s="10">
+        <v>2025</v>
+      </c>
+      <c r="T194" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="U194" s="45">
+        <v>208000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B195" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>974</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="G195" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="H195" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="I195" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="J195" s="9" t="s">
+        <v>977</v>
+      </c>
+      <c r="K195" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="L195" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="M195" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="N195" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O195" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P195" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q195" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="R195" s="11">
+        <v>45689</v>
+      </c>
+      <c r="S195" s="10">
+        <v>2025</v>
+      </c>
+      <c r="T195" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="U195" s="45">
+        <v>85980</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="197" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A197" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L197" s="3" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A198" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J198" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K198" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L198" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B199" s="6"/>
+      <c r="C199" s="29" t="s">
+        <v>983</v>
+      </c>
+      <c r="D199" s="30" t="s">
+        <v>984</v>
+      </c>
+      <c r="E199" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="F199" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G199" s="30" t="s">
+        <v>985</v>
+      </c>
+      <c r="H199" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="I199" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="J199" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="K199" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="L199" s="6"/>
+    </row>
+    <row r="200" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B200" s="6"/>
+      <c r="C200" s="29" t="s">
+        <v>988</v>
+      </c>
+      <c r="D200" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E200" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="F200" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G200" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="H200" s="30" t="s">
+        <v>989</v>
+      </c>
+      <c r="I200" s="31" t="s">
+        <v>990</v>
+      </c>
+      <c r="J200" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K200" s="30" t="s">
+        <v>991</v>
+      </c>
+      <c r="L200" s="6"/>
+    </row>
+    <row r="201" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B201" s="6"/>
+      <c r="C201" s="29" t="s">
+        <v>992</v>
+      </c>
+      <c r="D201" s="30" t="s">
+        <v>993</v>
+      </c>
+      <c r="E201" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="F201" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="G201" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="H201" s="30" t="s">
+        <v>994</v>
+      </c>
+      <c r="I201" s="31" t="s">
+        <v>995</v>
+      </c>
+      <c r="J201" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="K201" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="L201" s="6"/>
+    </row>
+    <row r="202" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B202" s="6"/>
+      <c r="C202" s="29" t="s">
+        <v>996</v>
+      </c>
+      <c r="D202" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E202" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F202" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G202" s="30" t="s">
+        <v>676</v>
+      </c>
+      <c r="H202" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="I202" s="31" t="s">
+        <v>998</v>
+      </c>
+      <c r="J202" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="K202" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="L202" s="42">
+        <v>29990</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B203" s="6"/>
+      <c r="C203" s="29" t="s">
+        <v>999</v>
+      </c>
+      <c r="D203" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E203" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="F203" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G203" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="H203" s="30" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I203" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="J203" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K203" s="30" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L203" s="6"/>
+    </row>
+    <row r="204" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A204" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B204" s="6"/>
+      <c r="C204" s="29" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D204" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E204" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F204" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G204" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H204" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="I204" s="31" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J204" s="30" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K204" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="L204" s="42">
+        <v>25780</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B205" s="6"/>
+      <c r="C205" s="29" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D205" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E205" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="F205" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G205" s="30" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H205" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I205" s="31" t="s">
+        <v>1008</v>
+      </c>
+      <c r="J205" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="K205" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="L205" s="42">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A206" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B206" s="6"/>
+      <c r="C206" s="29" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D206" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E206" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="F206" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G206" s="30" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H206" s="30" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I206" s="31" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J206" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K206" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="L206" s="6"/>
+    </row>
+    <row r="207" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="B207" s="48"/>
+      <c r="C207" s="47" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D207" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="E207" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="F207" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="G207" s="49" t="s">
+        <v>465</v>
+      </c>
+      <c r="H207" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="I207" s="50" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J207" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="K207" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="L207" s="51">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B208" s="6"/>
+      <c r="C208" s="29" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D208" s="30" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E208" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="F208" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G208" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="H208" s="30" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I208" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="J208" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="K208" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="L208" s="6"/>
+    </row>
+    <row r="209" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B209" s="52" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C209" s="29" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D209" s="30" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E209" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F209" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G209" s="30" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H209" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="I209" s="31" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J209" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K209" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="L209" s="42">
+        <v>52880</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B210" s="6"/>
+      <c r="C210" s="29" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D210" s="30" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E210" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="F210" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G210" s="30" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H210" s="30" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I210" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="J210" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="K210" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="L210" s="6"/>
+    </row>
+    <row r="211" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A211" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B211" s="6"/>
+      <c r="C211" s="29" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D211" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="E211" s="30" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F211" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G211" s="30" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H211" s="30" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I211" s="31" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J211" s="30" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K211" s="46" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L211" s="42">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A212" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B212" s="52" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C212" s="29" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D212" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="E212" s="30" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F212" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G212" s="30" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H212" s="30" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I212" s="31" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J212" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K212" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="L212" s="42">
+        <v>45880</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A213" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B213" s="6"/>
+      <c r="C213" s="29" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D213" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="E213" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F213" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G213" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H213" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="I213" s="31" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J213" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="K213" s="46" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L213" s="6"/>
+    </row>
+    <row r="214" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A214" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B214" s="6"/>
+      <c r="C214" s="29" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D214" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E214" s="46" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F214" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G214" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H214" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="I214" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="J214" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="K214" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="L214" s="42">
+        <v>27900</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A215" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B215" s="6"/>
+      <c r="C215" s="29" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D215" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E215" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="F215" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G215" s="30" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H215" s="30" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I215" s="31" t="s">
+        <v>1045</v>
+      </c>
+      <c r="J215" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K215" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="L215" s="6"/>
+    </row>
+    <row r="216" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A216" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B216" s="6"/>
+      <c r="C216" s="29" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D216" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E216" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="F216" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G216" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="H216" s="30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I216" s="31" t="s">
+        <v>1048</v>
+      </c>
+      <c r="J216" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K216" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="L216" s="6"/>
+    </row>
+    <row r="217" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B217" s="52" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C217" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D217" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E217" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F217" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G217" s="30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H217" s="30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I217" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="J217" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K217" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="L217" s="42">
+        <v>38880</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B218" s="6"/>
+      <c r="C218" s="29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D218" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E218" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F218" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="G218" s="30" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H218" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="I218" s="31" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J218" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="K218" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="L218" s="6"/>
+    </row>
+    <row r="219" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A219" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B219" s="6"/>
+      <c r="C219" s="29" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D219" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="E219" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="F219" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G219" s="30" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H219" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I219" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="J219" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="K219" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="L219" s="6"/>
+    </row>
+    <row r="220" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A220" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B220" s="6"/>
+      <c r="C220" s="29" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D220" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="E220" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="F220" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G220" s="30" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H220" s="30" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I220" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J220" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="K220" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="L220" s="6"/>
+    </row>
+    <row r="221" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="29" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B221" s="6"/>
+      <c r="C221" s="29" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D221" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="E221" s="46" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F221" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G221" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="H221" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="I221" s="31" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J221" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="K221" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="L221" s="42">
+        <v>23200</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A222" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B222" s="6"/>
+      <c r="C222" s="29" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D222" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="E222" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="F222" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G222" s="30" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H222" s="30" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I222" s="31" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J222" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="K222" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="L222" s="6"/>
+    </row>
+    <row r="223" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B223" s="6"/>
+      <c r="C223" s="29" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D223" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="E223" s="46" t="s">
+        <v>281</v>
+      </c>
+      <c r="F223" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G223" s="30" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H223" s="30" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I223" s="31" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J223" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="K223" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="L223" s="6"/>
+    </row>
+    <row r="224" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A224" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B224" s="52" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C224" s="29" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D224" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="E224" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F224" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G224" s="30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H224" s="30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I224" s="31" t="s">
+        <v>1069</v>
+      </c>
+      <c r="J224" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="K224" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="L224" s="42">
+        <v>29880</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A225" s="47" t="s">
+        <v>987</v>
+      </c>
+      <c r="B225" s="48"/>
+      <c r="C225" s="47" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D225" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="E225" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="F225" s="49" t="s">
+        <v>233</v>
+      </c>
+      <c r="G225" s="49" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H225" s="49" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I225" s="50" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J225" s="49" t="s">
+        <v>374</v>
+      </c>
+      <c r="K225" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="L225" s="48"/>
+    </row>
+    <row r="226" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A226" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B226" s="6"/>
+      <c r="C226" s="29" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D226" s="30" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E226" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F226" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="G226" s="30" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H226" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="I226" s="31" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J226" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="K226" s="46" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L226" s="6"/>
+    </row>
+    <row r="227" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A227" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B227" s="6"/>
+      <c r="C227" s="29" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D227" s="30" t="s">
+        <v>454</v>
+      </c>
+      <c r="E227" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F227" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G227" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="H227" s="30" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I227" s="31" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J227" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="K227" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="L227" s="6"/>
+    </row>
+    <row r="228" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A228" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B228" s="52" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C228" s="29" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D228" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="E228" s="30" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F228" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="G228" s="30" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H228" s="30" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I228" s="31" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J228" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="K228" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="L228" s="42">
+        <v>45800</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B229" s="6"/>
+      <c r="C229" s="29" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D229" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="E229" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="F229" s="30" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G229" s="30" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H229" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I229" s="31" t="s">
+        <v>1088</v>
+      </c>
+      <c r="J229" s="30" t="s">
+        <v>445</v>
+      </c>
+      <c r="K229" s="46" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L229" s="42">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A230" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B230" s="6"/>
+      <c r="C230" s="29" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D230" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="E230" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F230" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G230" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="H230" s="30" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I230" s="31" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J230" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="K230" s="46" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L230" s="42">
+        <v>15700</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A231" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B231" s="6"/>
+      <c r="C231" s="29" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D231" s="30" t="s">
+        <v>561</v>
+      </c>
+      <c r="E231" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="F231" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G231" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="H231" s="30" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I231" s="31" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J231" s="30" t="s">
+        <v>482</v>
+      </c>
+      <c r="K231" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="L231" s="42">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A232" s="29" t="s">
+        <v>987</v>
+      </c>
+      <c r="B232" s="6"/>
+      <c r="C232" s="29" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D232" s="30" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E232" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="F232" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G232" s="30" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H232" s="30" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I232" s="31" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J232" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="K232" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="L232" s="6"/>
+    </row>
+    <row r="233" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A233" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B233" s="48"/>
+      <c r="C233" s="47" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D233" s="49" t="s">
+        <v>570</v>
+      </c>
+      <c r="E233" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="F233" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="G233" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="H233" s="49" t="s">
+        <v>931</v>
+      </c>
+      <c r="I233" s="50" t="s">
+        <v>918</v>
+      </c>
+      <c r="J233" s="49" t="s">
+        <v>441</v>
+      </c>
+      <c r="K233" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="L233" s="48"/>
+    </row>
+    <row r="234" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B234" s="6"/>
+      <c r="C234" s="29" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D234" s="30" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E234" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="F234" s="30" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G234" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="H234" s="30" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I234" s="31" t="s">
+        <v>1105</v>
+      </c>
+      <c r="J234" s="30" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K234" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="L234" s="42">
+        <v>29300</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/sony lens.xlsx
+++ b/sony lens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\personl\camera\lenshistory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8244C07-3EC5-4DC6-9D8C-29D055063A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8300FF5-636C-40E4-A563-010A5EEA2BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prime_定焦鏡" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4534" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3127" uniqueCount="1106">
   <si>
     <t>廠牌</t>
   </si>
@@ -4051,7 +4051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U234"/>
+  <dimension ref="A1:T131"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:20" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="T128" s="6"/>
     </row>
-    <row r="129" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>58</v>
       </c>
@@ -11054,7 +11054,7 @@
       </c>
       <c r="T129" s="6"/>
     </row>
-    <row r="130" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>79</v>
       </c>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="T130" s="6"/>
     </row>
-    <row r="131" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
@@ -11135,5199 +11135,6 @@
       <c r="R131" s="6"/>
       <c r="S131" s="6"/>
       <c r="T131" s="6"/>
-    </row>
-    <row r="132" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="133" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M133" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N133" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O133" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P133" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q133" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R133" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S133" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T133" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U133" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="134" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F134" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I134" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J134" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K134" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L134" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M134" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N134" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O134" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P134" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q134" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="R134" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S134" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="T134" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="U134" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="135" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B135" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="D135" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E135" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="F135" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="G135" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I135" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="J135" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="K135" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="L135" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="M135" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="N135" s="1"/>
-      <c r="O135" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P135" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q135" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R135" s="11">
-        <v>44013</v>
-      </c>
-      <c r="S135" s="10">
-        <v>2020</v>
-      </c>
-      <c r="T135" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="U135" s="45">
-        <v>85980</v>
-      </c>
-    </row>
-    <row r="136" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B136" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D136" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E136" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="F136" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H136" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I136" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="J136" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="K136" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="L136" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="M136" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="N136" s="1"/>
-      <c r="O136" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P136" s="1"/>
-      <c r="Q136" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R136" s="11">
-        <v>42856</v>
-      </c>
-      <c r="S136" s="10">
-        <v>2017</v>
-      </c>
-      <c r="T136" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="U136" s="45">
-        <v>51980</v>
-      </c>
-    </row>
-    <row r="137" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B137" s="1"/>
-      <c r="C137" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="D137" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E137" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="G137" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I137" s="17" t="s">
-        <v>667</v>
-      </c>
-      <c r="J137" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="K137" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="L137" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="M137" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="N137" s="1"/>
-      <c r="O137" s="1"/>
-      <c r="P137" s="1"/>
-      <c r="Q137" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R137" s="11">
-        <v>45778</v>
-      </c>
-      <c r="S137" s="10">
-        <v>2025</v>
-      </c>
-      <c r="T137" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="U137" s="45">
-        <v>42990</v>
-      </c>
-    </row>
-    <row r="138" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B138" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E138" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="F138" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="G138" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H138" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I138" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="J138" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="K138" s="9" t="s">
-        <v>672</v>
-      </c>
-      <c r="L138" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="M138" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="N138" s="1"/>
-      <c r="O138" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P138" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q138" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R138" s="11">
-        <v>43709</v>
-      </c>
-      <c r="S138" s="10">
-        <v>2019</v>
-      </c>
-      <c r="T138" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="U138" s="45">
-        <v>43500</v>
-      </c>
-    </row>
-    <row r="139" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E139" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="F139" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="G139" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I139" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="J139" s="17" t="s">
-        <v>676</v>
-      </c>
-      <c r="K139" s="17" t="s">
-        <v>677</v>
-      </c>
-      <c r="L139" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="M139" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="N139" s="1"/>
-      <c r="O139" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P139" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q139" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R139" s="11">
-        <v>45383</v>
-      </c>
-      <c r="S139" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T139" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="U139" s="45">
-        <v>38980</v>
-      </c>
-    </row>
-    <row r="140" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B140" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E140" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="G140" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H140" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I140" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="J140" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="K140" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="L140" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="M140" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="N140" s="1"/>
-      <c r="O140" s="1"/>
-      <c r="P140" s="1"/>
-      <c r="Q140" s="1"/>
-      <c r="R140" s="11">
-        <v>44713</v>
-      </c>
-      <c r="S140" s="10">
-        <v>2022</v>
-      </c>
-      <c r="T140" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="U140" s="45">
-        <v>27800</v>
-      </c>
-    </row>
-    <row r="141" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B141" s="1"/>
-      <c r="C141" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E141" s="9" t="s">
-        <v>687</v>
-      </c>
-      <c r="F141" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="G141" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I141" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="J141" s="17" t="s">
-        <v>676</v>
-      </c>
-      <c r="K141" s="17" t="s">
-        <v>690</v>
-      </c>
-      <c r="L141" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M141" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N141" s="1"/>
-      <c r="O141" s="1"/>
-      <c r="P141" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q141" s="1"/>
-      <c r="R141" s="11">
-        <v>45839</v>
-      </c>
-      <c r="S141" s="10">
-        <v>2025</v>
-      </c>
-      <c r="T141" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="U141" s="45">
-        <v>29900</v>
-      </c>
-    </row>
-    <row r="142" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B142" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>692</v>
-      </c>
-      <c r="D142" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E142" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="F142" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="G142" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I142" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="J142" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="K142" s="9" t="s">
-        <v>697</v>
-      </c>
-      <c r="L142" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="M142" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N142" s="1"/>
-      <c r="O142" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P142" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q142" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R142" s="11">
-        <v>42856</v>
-      </c>
-      <c r="S142" s="10">
-        <v>2017</v>
-      </c>
-      <c r="T142" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="U142" s="45">
-        <v>67980</v>
-      </c>
-    </row>
-    <row r="143" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B143" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="D143" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E143" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="F143" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="G143" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I143" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="J143" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K143" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="L143" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="M143" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="N143" s="1"/>
-      <c r="O143" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P143" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q143" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R143" s="11">
-        <v>45139</v>
-      </c>
-      <c r="S143" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T143" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="U143" s="45">
-        <v>69980</v>
-      </c>
-    </row>
-    <row r="144" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B144" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>703</v>
-      </c>
-      <c r="D144" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E144" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="G144" s="10" t="s">
-        <v>704</v>
-      </c>
-      <c r="H144" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I144" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="J144" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="K144" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="L144" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="M144" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N144" s="1"/>
-      <c r="O144" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P144" s="1"/>
-      <c r="Q144" s="1"/>
-      <c r="R144" s="11">
-        <v>43709</v>
-      </c>
-      <c r="S144" s="10">
-        <v>2019</v>
-      </c>
-      <c r="T144" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="U144" s="45">
-        <v>179980</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B145" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="D145" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E145" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="F145" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I145" s="9" t="s">
-        <v>709</v>
-      </c>
-      <c r="J145" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="K145" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="L145" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="M145" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N145" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O145" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P145" s="1"/>
-      <c r="Q145" s="1"/>
-      <c r="R145" s="11">
-        <v>41760</v>
-      </c>
-      <c r="S145" s="10">
-        <v>2014</v>
-      </c>
-      <c r="T145" s="9" t="s">
-        <v>711</v>
-      </c>
-      <c r="U145" s="45">
-        <v>36980</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B146" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="D146" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E146" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="F146" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="G146" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H146" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I146" s="17" t="s">
-        <v>713</v>
-      </c>
-      <c r="J146" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="K146" s="17" t="s">
-        <v>715</v>
-      </c>
-      <c r="L146" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="M146" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="N146" s="1"/>
-      <c r="O146" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P146" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q146" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R146" s="11">
-        <v>44621</v>
-      </c>
-      <c r="S146" s="10">
-        <v>2022</v>
-      </c>
-      <c r="T146" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="U146" s="45">
-        <v>36980</v>
-      </c>
-    </row>
-    <row r="147" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B147" s="1"/>
-      <c r="C147" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="D147" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="E147" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="G147" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I147" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="J147" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="K147" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="L147" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M147" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N147" s="1"/>
-      <c r="O147" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P147" s="1"/>
-      <c r="Q147" s="1"/>
-      <c r="R147" s="11">
-        <v>43497</v>
-      </c>
-      <c r="S147" s="10">
-        <v>2019</v>
-      </c>
-      <c r="T147" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="U147" s="45">
-        <v>29200</v>
-      </c>
-    </row>
-    <row r="148" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B148" s="1"/>
-      <c r="C148" s="8" t="s">
-        <v>721</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="E148" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="F148" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G148" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H148" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I148" s="9" t="s">
-        <v>725</v>
-      </c>
-      <c r="J148" s="17" t="s">
-        <v>676</v>
-      </c>
-      <c r="K148" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="L148" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M148" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="N148" s="1"/>
-      <c r="O148" s="1"/>
-      <c r="P148" s="1"/>
-      <c r="Q148" s="1"/>
-      <c r="R148" s="11">
-        <v>45170</v>
-      </c>
-      <c r="S148" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T148" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="U148" s="45">
-        <v>24800</v>
-      </c>
-    </row>
-    <row r="149" spans="1:21" ht="130.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B149" s="1"/>
-      <c r="C149" s="8" t="s">
-        <v>726</v>
-      </c>
-      <c r="D149" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="E149" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="F149" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="G149" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I149" s="17" t="s">
-        <v>728</v>
-      </c>
-      <c r="J149" s="17" t="s">
-        <v>455</v>
-      </c>
-      <c r="K149" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="L149" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="M149" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="N149" s="1"/>
-      <c r="O149" s="1"/>
-      <c r="P149" s="1"/>
-      <c r="Q149" s="1"/>
-      <c r="R149" s="11">
-        <v>44774</v>
-      </c>
-      <c r="S149" s="10">
-        <v>2022</v>
-      </c>
-      <c r="T149" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="U149" s="45">
-        <v>24800</v>
-      </c>
-    </row>
-    <row r="150" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B150" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="E150" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="F150" s="17" t="s">
-        <v>731</v>
-      </c>
-      <c r="G150" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H150" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I150" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="J150" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="K150" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="L150" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="M150" s="17" t="s">
-        <v>732</v>
-      </c>
-      <c r="N150" s="1"/>
-      <c r="O150" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P150" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q150" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R150" s="11">
-        <v>44927</v>
-      </c>
-      <c r="S150" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T150" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="U150" s="45">
-        <v>33980</v>
-      </c>
-    </row>
-    <row r="151" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B151" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>734</v>
-      </c>
-      <c r="D151" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="E151" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="F151" s="17" t="s">
-        <v>737</v>
-      </c>
-      <c r="G151" s="10" t="s">
-        <v>738</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I151" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="J151" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="K151" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="L151" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="M151" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="N151" s="1"/>
-      <c r="O151" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P151" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q151" s="1"/>
-      <c r="R151" s="11">
-        <v>45901</v>
-      </c>
-      <c r="S151" s="10">
-        <v>2025</v>
-      </c>
-      <c r="T151" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="U151" s="45">
-        <v>29800</v>
-      </c>
-    </row>
-    <row r="152" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B152" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="D152" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E152" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="F152" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="G152" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H152" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I152" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="J152" s="17" t="s">
-        <v>676</v>
-      </c>
-      <c r="K152" s="17" t="s">
-        <v>690</v>
-      </c>
-      <c r="L152" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M152" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="N152" s="1"/>
-      <c r="O152" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P152" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q152" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R152" s="11">
-        <v>45323</v>
-      </c>
-      <c r="S152" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T152" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="U152" s="45">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="153" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B153" s="1"/>
-      <c r="C153" s="8" t="s">
-        <v>747</v>
-      </c>
-      <c r="D153" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E153" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="F153" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G153" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I153" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="J153" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="K153" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="L153" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="M153" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="N153" s="1"/>
-      <c r="O153" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P153" s="1"/>
-      <c r="Q153" s="1"/>
-      <c r="R153" s="11">
-        <v>44470</v>
-      </c>
-      <c r="S153" s="10">
-        <v>2021</v>
-      </c>
-      <c r="T153" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="U153" s="45">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="154" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B154" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E154" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="F154" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G154" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H154" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I154" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="J154" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K154" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="L154" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="M154" s="17" t="s">
-        <v>757</v>
-      </c>
-      <c r="N154" s="1"/>
-      <c r="O154" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P154" s="1"/>
-      <c r="Q154" s="1"/>
-      <c r="R154" s="11">
-        <v>43770</v>
-      </c>
-      <c r="S154" s="10">
-        <v>2019</v>
-      </c>
-      <c r="T154" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="U154" s="45">
-        <v>33900</v>
-      </c>
-    </row>
-    <row r="155" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B155" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>759</v>
-      </c>
-      <c r="D155" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E155" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="F155" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G155" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I155" s="9" t="s">
-        <v>760</v>
-      </c>
-      <c r="J155" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K155" s="9" t="s">
-        <v>761</v>
-      </c>
-      <c r="L155" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="M155" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="N155" s="1"/>
-      <c r="O155" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P155" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q155" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R155" s="11">
-        <v>45413</v>
-      </c>
-      <c r="S155" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T155" s="9" t="s">
-        <v>763</v>
-      </c>
-      <c r="U155" s="45">
-        <v>39880</v>
-      </c>
-    </row>
-    <row r="156" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B156" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="D156" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E156" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="F156" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G156" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H156" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I156" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="J156" s="9" t="s">
-        <v>765</v>
-      </c>
-      <c r="K156" s="9" t="s">
-        <v>766</v>
-      </c>
-      <c r="L156" s="9" t="s">
-        <v>767</v>
-      </c>
-      <c r="M156" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N156" s="1"/>
-      <c r="O156" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P156" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q156" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R156" s="11">
-        <v>42430</v>
-      </c>
-      <c r="S156" s="10">
-        <v>2016</v>
-      </c>
-      <c r="T156" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="U156" s="45">
-        <v>61980</v>
-      </c>
-    </row>
-    <row r="157" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B157" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E157" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="F157" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G157" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I157" s="9" t="s">
-        <v>769</v>
-      </c>
-      <c r="J157" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K157" s="9" t="s">
-        <v>770</v>
-      </c>
-      <c r="L157" s="9" t="s">
-        <v>771</v>
-      </c>
-      <c r="M157" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="N157" s="1"/>
-      <c r="O157" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P157" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q157" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R157" s="11">
-        <v>44652</v>
-      </c>
-      <c r="S157" s="10">
-        <v>2022</v>
-      </c>
-      <c r="T157" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="U157" s="45">
-        <v>55980</v>
-      </c>
-    </row>
-    <row r="158" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B158" s="35" t="s">
-        <v>324</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="D158" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E158" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="F158" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G158" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H158" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I158" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="J158" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="K158" s="17" t="s">
-        <v>774</v>
-      </c>
-      <c r="L158" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="M158" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="N158" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O158" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P158" s="1"/>
-      <c r="Q158" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R158" s="11">
-        <v>41640</v>
-      </c>
-      <c r="S158" s="10">
-        <v>2014</v>
-      </c>
-      <c r="T158" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="U158" s="45">
-        <v>28980</v>
-      </c>
-    </row>
-    <row r="159" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B159" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="D159" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E159" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="F159" s="17" t="s">
-        <v>779</v>
-      </c>
-      <c r="G159" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I159" s="9" t="s">
-        <v>780</v>
-      </c>
-      <c r="J159" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="K159" s="9" t="s">
-        <v>781</v>
-      </c>
-      <c r="L159" s="9" t="s">
-        <v>767</v>
-      </c>
-      <c r="M159" s="9" t="s">
-        <v>782</v>
-      </c>
-      <c r="N159" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O159" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P159" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q159" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R159" s="11">
-        <v>43009</v>
-      </c>
-      <c r="S159" s="10">
-        <v>2017</v>
-      </c>
-      <c r="T159" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="U159" s="45">
-        <v>41980</v>
-      </c>
-    </row>
-    <row r="160" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B160" s="1"/>
-      <c r="C160" s="8" t="s">
-        <v>783</v>
-      </c>
-      <c r="D160" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="E160" s="9" t="s">
-        <v>784</v>
-      </c>
-      <c r="F160" s="17" t="s">
-        <v>737</v>
-      </c>
-      <c r="G160" s="10" t="s">
-        <v>738</v>
-      </c>
-      <c r="H160" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I160" s="9" t="s">
-        <v>785</v>
-      </c>
-      <c r="J160" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="K160" s="9" t="s">
-        <v>786</v>
-      </c>
-      <c r="L160" s="9" t="s">
-        <v>787</v>
-      </c>
-      <c r="M160" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="N160" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O160" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P160" s="1"/>
-      <c r="Q160" s="1"/>
-      <c r="R160" s="11">
-        <v>42064</v>
-      </c>
-      <c r="S160" s="10">
-        <v>2015</v>
-      </c>
-      <c r="T160" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="U160" s="45">
-        <v>29980</v>
-      </c>
-    </row>
-    <row r="161" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B161" s="1"/>
-      <c r="C161" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="D161" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="E161" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="F161" s="17" t="s">
-        <v>790</v>
-      </c>
-      <c r="G161" s="10" t="s">
-        <v>791</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I161" s="9" t="s">
-        <v>792</v>
-      </c>
-      <c r="J161" s="9" t="s">
-        <v>793</v>
-      </c>
-      <c r="K161" s="9" t="s">
-        <v>794</v>
-      </c>
-      <c r="L161" s="9" t="s">
-        <v>795</v>
-      </c>
-      <c r="M161" s="17" t="s">
-        <v>796</v>
-      </c>
-      <c r="N161" s="1"/>
-      <c r="O161" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P161" s="1"/>
-      <c r="Q161" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R161" s="11">
-        <v>45931</v>
-      </c>
-      <c r="S161" s="10">
-        <v>2025</v>
-      </c>
-      <c r="T161" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="U161" s="1"/>
-    </row>
-    <row r="162" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B162" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="D162" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E162" s="9" t="s">
-        <v>799</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="G162" s="33" t="s">
-        <v>800</v>
-      </c>
-      <c r="H162" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I162" s="9" t="s">
-        <v>801</v>
-      </c>
-      <c r="J162" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K162" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="L162" s="9" t="s">
-        <v>802</v>
-      </c>
-      <c r="M162" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="N162" s="1"/>
-      <c r="O162" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P162" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q162" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R162" s="11">
-        <v>45444</v>
-      </c>
-      <c r="S162" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T162" s="9" t="s">
-        <v>763</v>
-      </c>
-      <c r="U162" s="45">
-        <v>45880</v>
-      </c>
-    </row>
-    <row r="163" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B163" s="1"/>
-      <c r="C163" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="D163" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E163" s="9" t="s">
-        <v>804</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="G163" s="10" t="s">
-        <v>805</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="I163" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="J163" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="K163" s="17" t="s">
-        <v>806</v>
-      </c>
-      <c r="L163" s="9" t="s">
-        <v>802</v>
-      </c>
-      <c r="M163" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="N163" s="1"/>
-      <c r="O163" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P163" s="1"/>
-      <c r="Q163" s="1"/>
-      <c r="R163" s="11">
-        <v>44075</v>
-      </c>
-      <c r="S163" s="10">
-        <v>2020</v>
-      </c>
-      <c r="T163" s="9" t="s">
-        <v>807</v>
-      </c>
-      <c r="U163" s="45">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="164" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B164" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="D164" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E164" s="9" t="s">
-        <v>809</v>
-      </c>
-      <c r="F164" s="9" t="s">
-        <v>810</v>
-      </c>
-      <c r="G164" s="33" t="s">
-        <v>811</v>
-      </c>
-      <c r="H164" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="I164" s="9" t="s">
-        <v>812</v>
-      </c>
-      <c r="J164" s="9" t="s">
-        <v>813</v>
-      </c>
-      <c r="K164" s="9" t="s">
-        <v>814</v>
-      </c>
-      <c r="L164" s="9" t="s">
-        <v>767</v>
-      </c>
-      <c r="M164" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="N164" s="1"/>
-      <c r="O164" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P164" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q164" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R164" s="11">
-        <v>45597</v>
-      </c>
-      <c r="S164" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T164" s="9" t="s">
-        <v>815</v>
-      </c>
-      <c r="U164" s="45">
-        <v>92980</v>
-      </c>
-    </row>
-    <row r="165" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B165" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>816</v>
-      </c>
-      <c r="D165" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E165" s="9" t="s">
-        <v>809</v>
-      </c>
-      <c r="F165" s="9" t="s">
-        <v>810</v>
-      </c>
-      <c r="G165" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H165" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I165" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="J165" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="K165" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="L165" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M165" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="N165" s="1"/>
-      <c r="O165" s="1"/>
-      <c r="P165" s="1"/>
-      <c r="Q165" s="1"/>
-      <c r="R165" s="11">
-        <v>44228</v>
-      </c>
-      <c r="S165" s="10">
-        <v>2021</v>
-      </c>
-      <c r="T165" s="9" t="s">
-        <v>818</v>
-      </c>
-      <c r="U165" s="45">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="166" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B166" s="1"/>
-      <c r="C166" s="8" t="s">
-        <v>819</v>
-      </c>
-      <c r="D166" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E166" s="9" t="s">
-        <v>809</v>
-      </c>
-      <c r="F166" s="9" t="s">
-        <v>810</v>
-      </c>
-      <c r="G166" s="10" t="s">
-        <v>820</v>
-      </c>
-      <c r="H166" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="I166" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="J166" s="17" t="s">
-        <v>821</v>
-      </c>
-      <c r="K166" s="17" t="s">
-        <v>343</v>
-      </c>
-      <c r="L166" s="9" t="s">
-        <v>802</v>
-      </c>
-      <c r="M166" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N166" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O166" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P166" s="1"/>
-      <c r="Q166" s="1"/>
-      <c r="R166" s="11">
-        <v>41548</v>
-      </c>
-      <c r="S166" s="10">
-        <v>2013</v>
-      </c>
-      <c r="T166" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="U166" s="45">
-        <v>14980</v>
-      </c>
-    </row>
-    <row r="167" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B167" s="1"/>
-      <c r="C167" s="8" t="s">
-        <v>822</v>
-      </c>
-      <c r="D167" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E167" s="9" t="s">
-        <v>823</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>824</v>
-      </c>
-      <c r="G167" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H167" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I167" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="J167" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="K167" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="L167" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M167" s="17" t="s">
-        <v>757</v>
-      </c>
-      <c r="N167" s="1"/>
-      <c r="O167" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P167" s="1"/>
-      <c r="Q167" s="1"/>
-      <c r="R167" s="11">
-        <v>43191</v>
-      </c>
-      <c r="S167" s="10">
-        <v>2018</v>
-      </c>
-      <c r="T167" s="9" t="s">
-        <v>826</v>
-      </c>
-      <c r="U167" s="45">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="168" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B168" s="1"/>
-      <c r="C168" s="8" t="s">
-        <v>827</v>
-      </c>
-      <c r="D168" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E168" s="9" t="s">
-        <v>823</v>
-      </c>
-      <c r="F168" s="9" t="s">
-        <v>824</v>
-      </c>
-      <c r="G168" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H168" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I168" s="9" t="s">
-        <v>828</v>
-      </c>
-      <c r="J168" s="9" t="s">
-        <v>829</v>
-      </c>
-      <c r="K168" s="9" t="s">
-        <v>830</v>
-      </c>
-      <c r="L168" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="M168" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="N168" s="1"/>
-      <c r="O168" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P168" s="1"/>
-      <c r="Q168" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R168" s="11">
-        <v>44470</v>
-      </c>
-      <c r="S168" s="10">
-        <v>2021</v>
-      </c>
-      <c r="T168" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="U168" s="45">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="169" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B169" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>831</v>
-      </c>
-      <c r="D169" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E169" s="9" t="s">
-        <v>832</v>
-      </c>
-      <c r="F169" s="17" t="s">
-        <v>833</v>
-      </c>
-      <c r="G169" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H169" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I169" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="J169" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K169" s="9" t="s">
-        <v>834</v>
-      </c>
-      <c r="L169" s="9" t="s">
-        <v>835</v>
-      </c>
-      <c r="M169" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="N169" s="1"/>
-      <c r="O169" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P169" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q169" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R169" s="11">
-        <v>45536</v>
-      </c>
-      <c r="S169" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T169" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="U169" s="45">
-        <v>52600</v>
-      </c>
-    </row>
-    <row r="170" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B170" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>836</v>
-      </c>
-      <c r="D170" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E170" s="9" t="s">
-        <v>837</v>
-      </c>
-      <c r="F170" s="17" t="s">
-        <v>838</v>
-      </c>
-      <c r="G170" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H170" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="I170" s="9" t="s">
-        <v>839</v>
-      </c>
-      <c r="J170" s="9" t="s">
-        <v>840</v>
-      </c>
-      <c r="K170" s="9" t="s">
-        <v>841</v>
-      </c>
-      <c r="L170" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="M170" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="N170" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O170" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P170" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q170" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R170" s="11">
-        <v>41883</v>
-      </c>
-      <c r="S170" s="10">
-        <v>2014</v>
-      </c>
-      <c r="T170" s="9" t="s">
-        <v>842</v>
-      </c>
-      <c r="U170" s="45">
-        <v>74980</v>
-      </c>
-    </row>
-    <row r="171" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B171" s="1"/>
-      <c r="C171" s="8" t="s">
-        <v>843</v>
-      </c>
-      <c r="D171" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="E171" s="9" t="s">
-        <v>844</v>
-      </c>
-      <c r="F171" s="17" t="s">
-        <v>845</v>
-      </c>
-      <c r="G171" s="10" t="s">
-        <v>791</v>
-      </c>
-      <c r="H171" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I171" s="9" t="s">
-        <v>846</v>
-      </c>
-      <c r="J171" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="K171" s="9" t="s">
-        <v>794</v>
-      </c>
-      <c r="L171" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M171" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="N171" s="1"/>
-      <c r="O171" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P171" s="1"/>
-      <c r="Q171" s="1"/>
-      <c r="R171" s="11">
-        <v>43983</v>
-      </c>
-      <c r="S171" s="10">
-        <v>2020</v>
-      </c>
-      <c r="T171" s="9" t="s">
-        <v>847</v>
-      </c>
-      <c r="U171" s="45">
-        <v>20800</v>
-      </c>
-    </row>
-    <row r="172" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B172" s="1"/>
-      <c r="C172" s="8" t="s">
-        <v>848</v>
-      </c>
-      <c r="D172" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="E172" s="9" t="s">
-        <v>849</v>
-      </c>
-      <c r="F172" s="17" t="s">
-        <v>850</v>
-      </c>
-      <c r="G172" s="10" t="s">
-        <v>851</v>
-      </c>
-      <c r="H172" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I172" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J172" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="K172" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="L172" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="M172" s="17" t="s">
-        <v>853</v>
-      </c>
-      <c r="N172" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O172" s="1"/>
-      <c r="P172" s="1"/>
-      <c r="Q172" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R172" s="11">
-        <v>45474</v>
-      </c>
-      <c r="S172" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T172" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="U172" s="45">
-        <v>29800</v>
-      </c>
-    </row>
-    <row r="173" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B173" s="1"/>
-      <c r="C173" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="D173" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E173" s="9" t="s">
-        <v>855</v>
-      </c>
-      <c r="F173" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G173" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H173" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I173" s="9" t="s">
-        <v>856</v>
-      </c>
-      <c r="J173" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="K173" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="L173" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="M173" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="N173" s="1"/>
-      <c r="O173" s="1"/>
-      <c r="P173" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q173" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R173" s="11">
-        <v>46054</v>
-      </c>
-      <c r="S173" s="10">
-        <v>2026</v>
-      </c>
-      <c r="T173" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="U173" s="45">
-        <v>34000</v>
-      </c>
-    </row>
-    <row r="174" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B174" s="1"/>
-      <c r="C174" s="8" t="s">
-        <v>857</v>
-      </c>
-      <c r="D174" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E174" s="9" t="s">
-        <v>858</v>
-      </c>
-      <c r="F174" s="17" t="s">
-        <v>859</v>
-      </c>
-      <c r="G174" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="H174" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I174" s="9" t="s">
-        <v>861</v>
-      </c>
-      <c r="J174" s="9" t="s">
-        <v>862</v>
-      </c>
-      <c r="K174" s="9" t="s">
-        <v>863</v>
-      </c>
-      <c r="L174" s="9" t="s">
-        <v>864</v>
-      </c>
-      <c r="M174" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="N174" s="1"/>
-      <c r="O174" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P174" s="1"/>
-      <c r="Q174" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R174" s="11">
-        <v>45017</v>
-      </c>
-      <c r="S174" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T174" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="U174" s="45">
-        <v>34600</v>
-      </c>
-    </row>
-    <row r="175" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B175" s="1"/>
-      <c r="C175" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E175" s="9" t="s">
-        <v>858</v>
-      </c>
-      <c r="F175" s="17" t="s">
-        <v>859</v>
-      </c>
-      <c r="G175" s="14" t="s">
-        <v>860</v>
-      </c>
-      <c r="H175" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I175" s="9" t="s">
-        <v>866</v>
-      </c>
-      <c r="J175" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="K175" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="L175" s="9" t="s">
-        <v>868</v>
-      </c>
-      <c r="M175" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="N175" s="1"/>
-      <c r="O175" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P175" s="1"/>
-      <c r="Q175" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R175" s="11">
-        <v>44470</v>
-      </c>
-      <c r="S175" s="10">
-        <v>2021</v>
-      </c>
-      <c r="T175" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="U175" s="45">
-        <v>45800</v>
-      </c>
-    </row>
-    <row r="176" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B176" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>869</v>
-      </c>
-      <c r="D176" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E176" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="F176" s="17" t="s">
-        <v>871</v>
-      </c>
-      <c r="G176" s="33" t="s">
-        <v>811</v>
-      </c>
-      <c r="H176" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="I176" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="J176" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="K176" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="L176" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="M176" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="N176" s="1"/>
-      <c r="O176" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P176" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q176" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R176" s="11">
-        <v>45748</v>
-      </c>
-      <c r="S176" s="10">
-        <v>2025</v>
-      </c>
-      <c r="T176" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="U176" s="45">
-        <v>116980</v>
-      </c>
-    </row>
-    <row r="177" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B177" s="1"/>
-      <c r="C177" s="8" t="s">
-        <v>875</v>
-      </c>
-      <c r="D177" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="E177" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="F177" s="17" t="s">
-        <v>877</v>
-      </c>
-      <c r="G177" s="10" t="s">
-        <v>878</v>
-      </c>
-      <c r="H177" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I177" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="J177" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="K177" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="L177" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="M177" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="N177" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O177" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P177" s="1"/>
-      <c r="Q177" s="1"/>
-      <c r="R177" s="11">
-        <v>45444</v>
-      </c>
-      <c r="S177" s="10">
-        <v>2024</v>
-      </c>
-      <c r="T177" s="9" t="s">
-        <v>880</v>
-      </c>
-      <c r="U177" s="45">
-        <v>26800</v>
-      </c>
-    </row>
-    <row r="178" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B178" s="1"/>
-      <c r="C178" s="8" t="s">
-        <v>881</v>
-      </c>
-      <c r="D178" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="E178" s="9" t="s">
-        <v>882</v>
-      </c>
-      <c r="F178" s="17" t="s">
-        <v>790</v>
-      </c>
-      <c r="G178" s="10" t="s">
-        <v>878</v>
-      </c>
-      <c r="H178" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I178" s="9" t="s">
-        <v>883</v>
-      </c>
-      <c r="J178" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="K178" s="9" t="s">
-        <v>884</v>
-      </c>
-      <c r="L178" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="M178" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="N178" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O178" s="1"/>
-      <c r="P178" s="1"/>
-      <c r="Q178" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R178" s="11">
-        <v>44774</v>
-      </c>
-      <c r="S178" s="10">
-        <v>2022</v>
-      </c>
-      <c r="T178" s="9" t="s">
-        <v>885</v>
-      </c>
-      <c r="U178" s="45">
-        <v>40800</v>
-      </c>
-    </row>
-    <row r="179" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B179" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>886</v>
-      </c>
-      <c r="D179" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="E179" s="9" t="s">
-        <v>887</v>
-      </c>
-      <c r="F179" s="17" t="s">
-        <v>737</v>
-      </c>
-      <c r="G179" s="10" t="s">
-        <v>878</v>
-      </c>
-      <c r="H179" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="I179" s="9" t="s">
-        <v>888</v>
-      </c>
-      <c r="J179" s="9" t="s">
-        <v>889</v>
-      </c>
-      <c r="K179" s="9" t="s">
-        <v>890</v>
-      </c>
-      <c r="L179" s="9" t="s">
-        <v>891</v>
-      </c>
-      <c r="M179" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="N179" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O179" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P179" s="1"/>
-      <c r="Q179" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R179" s="11">
-        <v>44927</v>
-      </c>
-      <c r="S179" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T179" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="U179" s="45">
-        <v>64900</v>
-      </c>
-    </row>
-    <row r="180" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B180" s="1"/>
-      <c r="C180" s="8" t="s">
-        <v>892</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>894</v>
-      </c>
-      <c r="F180" s="9" t="s">
-        <v>895</v>
-      </c>
-      <c r="G180" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H180" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I180" s="9" t="s">
-        <v>896</v>
-      </c>
-      <c r="J180" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="K180" s="9" t="s">
-        <v>897</v>
-      </c>
-      <c r="L180" s="9" t="s">
-        <v>898</v>
-      </c>
-      <c r="M180" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="N180" s="1"/>
-      <c r="O180" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P180" s="1"/>
-      <c r="Q180" s="1"/>
-      <c r="R180" s="11">
-        <v>43739</v>
-      </c>
-      <c r="S180" s="10">
-        <v>2019</v>
-      </c>
-      <c r="T180" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="U180" s="45">
-        <v>35800</v>
-      </c>
-    </row>
-    <row r="181" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A181" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B181" s="1"/>
-      <c r="C181" s="8" t="s">
-        <v>899</v>
-      </c>
-      <c r="D181" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E181" s="9" t="s">
-        <v>894</v>
-      </c>
-      <c r="F181" s="9" t="s">
-        <v>895</v>
-      </c>
-      <c r="G181" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H181" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I181" s="9" t="s">
-        <v>900</v>
-      </c>
-      <c r="J181" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K181" s="9" t="s">
-        <v>901</v>
-      </c>
-      <c r="L181" s="9" t="s">
-        <v>802</v>
-      </c>
-      <c r="M181" s="17" t="s">
-        <v>902</v>
-      </c>
-      <c r="N181" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O181" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P181" s="1"/>
-      <c r="Q181" s="1"/>
-      <c r="R181" s="11">
-        <v>45170</v>
-      </c>
-      <c r="S181" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T181" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="U181" s="45">
-        <v>41000</v>
-      </c>
-    </row>
-    <row r="182" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B182" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>903</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E182" s="9" t="s">
-        <v>904</v>
-      </c>
-      <c r="F182" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G182" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H182" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I182" s="9" t="s">
-        <v>905</v>
-      </c>
-      <c r="J182" s="9" t="s">
-        <v>906</v>
-      </c>
-      <c r="K182" s="9" t="s">
-        <v>907</v>
-      </c>
-      <c r="L182" s="9" t="s">
-        <v>908</v>
-      </c>
-      <c r="M182" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N182" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O182" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P182" s="1"/>
-      <c r="Q182" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R182" s="11">
-        <v>45231</v>
-      </c>
-      <c r="S182" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T182" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="U182" s="45">
-        <v>49800</v>
-      </c>
-    </row>
-    <row r="183" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B183" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>909</v>
-      </c>
-      <c r="D183" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E183" s="9" t="s">
-        <v>904</v>
-      </c>
-      <c r="F183" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G183" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H183" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I183" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="J183" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="K183" s="9" t="s">
-        <v>910</v>
-      </c>
-      <c r="L183" s="9" t="s">
-        <v>911</v>
-      </c>
-      <c r="M183" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="N183" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O183" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P183" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q183" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R183" s="11">
-        <v>42401</v>
-      </c>
-      <c r="S183" s="10">
-        <v>2016</v>
-      </c>
-      <c r="T183" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="U183" s="45">
-        <v>76980</v>
-      </c>
-    </row>
-    <row r="184" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B184" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C184" s="8" t="s">
-        <v>913</v>
-      </c>
-      <c r="D184" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E184" s="9" t="s">
-        <v>904</v>
-      </c>
-      <c r="F184" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G184" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="H184" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I184" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="J184" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="K184" s="9" t="s">
-        <v>914</v>
-      </c>
-      <c r="L184" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="M184" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="N184" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O184" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P184" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q184" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R184" s="11">
-        <v>44531</v>
-      </c>
-      <c r="S184" s="10">
-        <v>2021</v>
-      </c>
-      <c r="T184" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="U184" s="45">
-        <v>76980</v>
-      </c>
-    </row>
-    <row r="185" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B185" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>916</v>
-      </c>
-      <c r="D185" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E185" s="9" t="s">
-        <v>904</v>
-      </c>
-      <c r="F185" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G185" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H185" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I185" s="9" t="s">
-        <v>917</v>
-      </c>
-      <c r="J185" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="K185" s="9" t="s">
-        <v>918</v>
-      </c>
-      <c r="L185" s="9" t="s">
-        <v>919</v>
-      </c>
-      <c r="M185" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="N185" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O185" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P185" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q185" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R185" s="11">
-        <v>42552</v>
-      </c>
-      <c r="S185" s="10">
-        <v>2016</v>
-      </c>
-      <c r="T185" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="U185" s="45">
-        <v>42980</v>
-      </c>
-    </row>
-    <row r="186" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B186" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>920</v>
-      </c>
-      <c r="D186" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E186" s="9" t="s">
-        <v>904</v>
-      </c>
-      <c r="F186" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="G186" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H186" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I186" s="9" t="s">
-        <v>896</v>
-      </c>
-      <c r="J186" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K186" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="L186" s="9" t="s">
-        <v>922</v>
-      </c>
-      <c r="M186" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="N186" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O186" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P186" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q186" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R186" s="11">
-        <v>45108</v>
-      </c>
-      <c r="S186" s="10">
-        <v>2023</v>
-      </c>
-      <c r="T186" s="9" t="s">
-        <v>923</v>
-      </c>
-      <c r="U186" s="45">
-        <v>47980</v>
-      </c>
-    </row>
-    <row r="187" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B187" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>924</v>
-      </c>
-      <c r="D187" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E187" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="F187" s="17" t="s">
-        <v>859</v>
-      </c>
-      <c r="G187" s="10" t="s">
-        <v>926</v>
-      </c>
-      <c r="H187" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I187" s="9" t="s">
-        <v>927</v>
-      </c>
-      <c r="J187" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="K187" s="9" t="s">
-        <v>928</v>
-      </c>
-      <c r="L187" s="9" t="s">
-        <v>929</v>
-      </c>
-      <c r="M187" s="9" t="s">
-        <v>782</v>
-      </c>
-      <c r="N187" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O187" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P187" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q187" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R187" s="11">
-        <v>42430</v>
-      </c>
-      <c r="S187" s="10">
-        <v>2016</v>
-      </c>
-      <c r="T187" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="U187" s="45">
-        <v>35980</v>
-      </c>
-    </row>
-    <row r="188" spans="1:21" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B188" s="1"/>
-      <c r="C188" s="8" t="s">
-        <v>930</v>
-      </c>
-      <c r="D188" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E188" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="F188" s="17" t="s">
-        <v>859</v>
-      </c>
-      <c r="G188" s="10" t="s">
-        <v>878</v>
-      </c>
-      <c r="H188" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I188" s="9" t="s">
-        <v>931</v>
-      </c>
-      <c r="J188" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="K188" s="9" t="s">
-        <v>932</v>
-      </c>
-      <c r="L188" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="M188" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="N188" s="1"/>
-      <c r="O188" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P188" s="1"/>
-      <c r="Q188" s="1"/>
-      <c r="R188" s="11">
-        <v>44075</v>
-      </c>
-      <c r="S188" s="10">
-        <v>2020</v>
-      </c>
-      <c r="T188" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="U188" s="45">
-        <v>13600</v>
-      </c>
-    </row>
-    <row r="189" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B189" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="D189" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E189" s="9" t="s">
-        <v>935</v>
-      </c>
-      <c r="F189" s="17" t="s">
-        <v>936</v>
-      </c>
-      <c r="G189" s="10" t="s">
-        <v>926</v>
-      </c>
-      <c r="H189" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I189" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="J189" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="K189" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="L189" s="9" t="s">
-        <v>940</v>
-      </c>
-      <c r="M189" s="17" t="s">
-        <v>941</v>
-      </c>
-      <c r="N189" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O189" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P189" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q189" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R189" s="11">
-        <v>42826</v>
-      </c>
-      <c r="S189" s="10">
-        <v>2017</v>
-      </c>
-      <c r="T189" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="U189" s="45">
-        <v>75980</v>
-      </c>
-    </row>
-    <row r="190" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B190" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C190" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="D190" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E190" s="9" t="s">
-        <v>935</v>
-      </c>
-      <c r="F190" s="17" t="s">
-        <v>936</v>
-      </c>
-      <c r="G190" s="10" t="s">
-        <v>943</v>
-      </c>
-      <c r="H190" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I190" s="9" t="s">
-        <v>944</v>
-      </c>
-      <c r="J190" s="9" t="s">
-        <v>945</v>
-      </c>
-      <c r="K190" s="9" t="s">
-        <v>946</v>
-      </c>
-      <c r="L190" s="9" t="s">
-        <v>947</v>
-      </c>
-      <c r="M190" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N190" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O190" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P190" s="1"/>
-      <c r="Q190" s="1"/>
-      <c r="R190" s="11">
-        <v>43983</v>
-      </c>
-      <c r="S190" s="10">
-        <v>2020</v>
-      </c>
-      <c r="T190" s="9" t="s">
-        <v>847</v>
-      </c>
-      <c r="U190" s="45">
-        <v>27800</v>
-      </c>
-    </row>
-    <row r="191" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B191" s="1"/>
-      <c r="C191" s="8" t="s">
-        <v>948</v>
-      </c>
-      <c r="D191" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E191" s="9" t="s">
-        <v>949</v>
-      </c>
-      <c r="F191" s="17" t="s">
-        <v>950</v>
-      </c>
-      <c r="G191" s="10" t="s">
-        <v>951</v>
-      </c>
-      <c r="H191" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I191" s="9" t="s">
-        <v>952</v>
-      </c>
-      <c r="J191" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="K191" s="9" t="s">
-        <v>953</v>
-      </c>
-      <c r="L191" s="9" t="s">
-        <v>891</v>
-      </c>
-      <c r="M191" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="N191" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O191" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P191" s="1"/>
-      <c r="Q191" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R191" s="11">
-        <v>44287</v>
-      </c>
-      <c r="S191" s="10">
-        <v>2021</v>
-      </c>
-      <c r="T191" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="U191" s="45">
-        <v>36800</v>
-      </c>
-    </row>
-    <row r="192" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B192" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C192" s="8" t="s">
-        <v>954</v>
-      </c>
-      <c r="D192" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E192" s="9" t="s">
-        <v>955</v>
-      </c>
-      <c r="F192" s="17" t="s">
-        <v>936</v>
-      </c>
-      <c r="G192" s="10" t="s">
-        <v>956</v>
-      </c>
-      <c r="H192" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="I192" s="9" t="s">
-        <v>957</v>
-      </c>
-      <c r="J192" s="9" t="s">
-        <v>958</v>
-      </c>
-      <c r="K192" s="9" t="s">
-        <v>959</v>
-      </c>
-      <c r="L192" s="9" t="s">
-        <v>960</v>
-      </c>
-      <c r="M192" s="17" t="s">
-        <v>757</v>
-      </c>
-      <c r="N192" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O192" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P192" s="1"/>
-      <c r="Q192" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R192" s="11">
-        <v>44409</v>
-      </c>
-      <c r="S192" s="10">
-        <v>2021</v>
-      </c>
-      <c r="T192" s="9" t="s">
-        <v>961</v>
-      </c>
-      <c r="U192" s="45">
-        <v>39900</v>
-      </c>
-    </row>
-    <row r="193" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B193" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C193" s="8" t="s">
-        <v>962</v>
-      </c>
-      <c r="D193" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E193" s="9" t="s">
-        <v>963</v>
-      </c>
-      <c r="F193" s="17" t="s">
-        <v>871</v>
-      </c>
-      <c r="G193" s="10" t="s">
-        <v>943</v>
-      </c>
-      <c r="H193" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="I193" s="9" t="s">
-        <v>964</v>
-      </c>
-      <c r="J193" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="K193" s="9" t="s">
-        <v>965</v>
-      </c>
-      <c r="L193" s="9" t="s">
-        <v>966</v>
-      </c>
-      <c r="M193" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="N193" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O193" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P193" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q193" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R193" s="11">
-        <v>43617</v>
-      </c>
-      <c r="S193" s="10">
-        <v>2019</v>
-      </c>
-      <c r="T193" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="U193" s="45">
-        <v>57980</v>
-      </c>
-    </row>
-    <row r="194" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B194" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C194" s="8" t="s">
-        <v>967</v>
-      </c>
-      <c r="D194" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E194" s="9" t="s">
-        <v>968</v>
-      </c>
-      <c r="F194" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="G194" s="10" t="s">
-        <v>660</v>
-      </c>
-      <c r="H194" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I194" s="9" t="s">
-        <v>969</v>
-      </c>
-      <c r="J194" s="9" t="s">
-        <v>970</v>
-      </c>
-      <c r="K194" s="9" t="s">
-        <v>971</v>
-      </c>
-      <c r="L194" s="9" t="s">
-        <v>972</v>
-      </c>
-      <c r="M194" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="N194" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O194" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P194" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q194" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R194" s="11">
-        <v>45689</v>
-      </c>
-      <c r="S194" s="10">
-        <v>2025</v>
-      </c>
-      <c r="T194" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="U194" s="45">
-        <v>208000</v>
-      </c>
-    </row>
-    <row r="195" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B195" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C195" s="8" t="s">
-        <v>973</v>
-      </c>
-      <c r="D195" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="E195" s="9" t="s">
-        <v>974</v>
-      </c>
-      <c r="F195" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="G195" s="10" t="s">
-        <v>975</v>
-      </c>
-      <c r="H195" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="I195" s="9" t="s">
-        <v>976</v>
-      </c>
-      <c r="J195" s="9" t="s">
-        <v>977</v>
-      </c>
-      <c r="K195" s="9" t="s">
-        <v>978</v>
-      </c>
-      <c r="L195" s="9" t="s">
-        <v>979</v>
-      </c>
-      <c r="M195" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="N195" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O195" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P195" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q195" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="R195" s="11">
-        <v>45689</v>
-      </c>
-      <c r="S195" s="10">
-        <v>2025</v>
-      </c>
-      <c r="T195" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="U195" s="45">
-        <v>85980</v>
-      </c>
-    </row>
-    <row r="196" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="197" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H197" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I197" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J197" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K197" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L197" s="3" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="198" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A198" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E198" s="4" t="s">
-        <v>982</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G198" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H198" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I198" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J198" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K198" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L198" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="199" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B199" s="6"/>
-      <c r="C199" s="29" t="s">
-        <v>983</v>
-      </c>
-      <c r="D199" s="30" t="s">
-        <v>984</v>
-      </c>
-      <c r="E199" s="30" t="s">
-        <v>631</v>
-      </c>
-      <c r="F199" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G199" s="30" t="s">
-        <v>985</v>
-      </c>
-      <c r="H199" s="30" t="s">
-        <v>986</v>
-      </c>
-      <c r="I199" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="J199" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="K199" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="L199" s="6"/>
-    </row>
-    <row r="200" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B200" s="6"/>
-      <c r="C200" s="29" t="s">
-        <v>988</v>
-      </c>
-      <c r="D200" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="E200" s="30" t="s">
-        <v>631</v>
-      </c>
-      <c r="F200" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G200" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="H200" s="30" t="s">
-        <v>989</v>
-      </c>
-      <c r="I200" s="31" t="s">
-        <v>990</v>
-      </c>
-      <c r="J200" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="K200" s="30" t="s">
-        <v>991</v>
-      </c>
-      <c r="L200" s="6"/>
-    </row>
-    <row r="201" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B201" s="6"/>
-      <c r="C201" s="29" t="s">
-        <v>992</v>
-      </c>
-      <c r="D201" s="30" t="s">
-        <v>993</v>
-      </c>
-      <c r="E201" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="F201" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="G201" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="H201" s="30" t="s">
-        <v>994</v>
-      </c>
-      <c r="I201" s="31" t="s">
-        <v>995</v>
-      </c>
-      <c r="J201" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="K201" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="L201" s="6"/>
-    </row>
-    <row r="202" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B202" s="6"/>
-      <c r="C202" s="29" t="s">
-        <v>996</v>
-      </c>
-      <c r="D202" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E202" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F202" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G202" s="30" t="s">
-        <v>676</v>
-      </c>
-      <c r="H202" s="30" t="s">
-        <v>997</v>
-      </c>
-      <c r="I202" s="31" t="s">
-        <v>998</v>
-      </c>
-      <c r="J202" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="K202" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="L202" s="42">
-        <v>29990</v>
-      </c>
-    </row>
-    <row r="203" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B203" s="6"/>
-      <c r="C203" s="29" t="s">
-        <v>999</v>
-      </c>
-      <c r="D203" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E203" s="30" t="s">
-        <v>631</v>
-      </c>
-      <c r="F203" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G203" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="H203" s="30" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I203" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="J203" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="K203" s="30" t="s">
-        <v>1001</v>
-      </c>
-      <c r="L203" s="6"/>
-    </row>
-    <row r="204" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B204" s="6"/>
-      <c r="C204" s="29" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D204" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E204" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="F204" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G204" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="H204" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="I204" s="31" t="s">
-        <v>1003</v>
-      </c>
-      <c r="J204" s="30" t="s">
-        <v>1004</v>
-      </c>
-      <c r="K204" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="L204" s="42">
-        <v>25780</v>
-      </c>
-    </row>
-    <row r="205" spans="1:21" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B205" s="6"/>
-      <c r="C205" s="29" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D205" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E205" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="F205" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="G205" s="30" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H205" s="30" t="s">
-        <v>1007</v>
-      </c>
-      <c r="I205" s="31" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J205" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="K205" s="46" t="s">
-        <v>446</v>
-      </c>
-      <c r="L205" s="42">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="206" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B206" s="6"/>
-      <c r="C206" s="29" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D206" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E206" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="F206" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G206" s="30" t="s">
-        <v>1010</v>
-      </c>
-      <c r="H206" s="30" t="s">
-        <v>1011</v>
-      </c>
-      <c r="I206" s="31" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J206" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="K206" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="L206" s="6"/>
-    </row>
-    <row r="207" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="B207" s="48"/>
-      <c r="C207" s="47" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D207" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="E207" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="F207" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="G207" s="49" t="s">
-        <v>465</v>
-      </c>
-      <c r="H207" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="I207" s="50" t="s">
-        <v>1014</v>
-      </c>
-      <c r="J207" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="K207" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="L207" s="51">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="208" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B208" s="6"/>
-      <c r="C208" s="29" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D208" s="30" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E208" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="F208" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="G208" s="30" t="s">
-        <v>449</v>
-      </c>
-      <c r="H208" s="30" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I208" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="J208" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="K208" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="L208" s="6"/>
-    </row>
-    <row r="209" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A209" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B209" s="52" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C209" s="29" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D209" s="30" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E209" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F209" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="G209" s="30" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H209" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="I209" s="31" t="s">
-        <v>1021</v>
-      </c>
-      <c r="J209" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="K209" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="L209" s="42">
-        <v>52880</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B210" s="6"/>
-      <c r="C210" s="29" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D210" s="30" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E210" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="F210" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="G210" s="30" t="s">
-        <v>1023</v>
-      </c>
-      <c r="H210" s="30" t="s">
-        <v>1024</v>
-      </c>
-      <c r="I210" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="J210" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="K210" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="L210" s="6"/>
-    </row>
-    <row r="211" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B211" s="6"/>
-      <c r="C211" s="29" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D211" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="E211" s="30" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F211" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G211" s="30" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H211" s="30" t="s">
-        <v>1028</v>
-      </c>
-      <c r="I211" s="31" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J211" s="30" t="s">
-        <v>1030</v>
-      </c>
-      <c r="K211" s="46" t="s">
-        <v>1031</v>
-      </c>
-      <c r="L211" s="42">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="212" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B212" s="52" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C212" s="29" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D212" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="E212" s="30" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F212" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="G212" s="30" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H212" s="30" t="s">
-        <v>1034</v>
-      </c>
-      <c r="I212" s="31" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J212" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="K212" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="L212" s="42">
-        <v>45880</v>
-      </c>
-    </row>
-    <row r="213" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A213" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B213" s="6"/>
-      <c r="C213" s="29" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D213" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="E213" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F213" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G213" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="H213" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="I213" s="31" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J213" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="K213" s="46" t="s">
-        <v>1038</v>
-      </c>
-      <c r="L213" s="6"/>
-    </row>
-    <row r="214" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B214" s="6"/>
-      <c r="C214" s="29" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D214" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E214" s="46" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F214" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="G214" s="30" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H214" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="I214" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="J214" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="K214" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="L214" s="42">
-        <v>27900</v>
-      </c>
-    </row>
-    <row r="215" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B215" s="6"/>
-      <c r="C215" s="29" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D215" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E215" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="F215" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G215" s="30" t="s">
-        <v>1043</v>
-      </c>
-      <c r="H215" s="30" t="s">
-        <v>1044</v>
-      </c>
-      <c r="I215" s="31" t="s">
-        <v>1045</v>
-      </c>
-      <c r="J215" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="K215" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="L215" s="6"/>
-    </row>
-    <row r="216" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B216" s="6"/>
-      <c r="C216" s="29" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D216" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E216" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="F216" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G216" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="H216" s="30" t="s">
-        <v>1047</v>
-      </c>
-      <c r="I216" s="31" t="s">
-        <v>1048</v>
-      </c>
-      <c r="J216" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="K216" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="L216" s="6"/>
-    </row>
-    <row r="217" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B217" s="52" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C217" s="29" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D217" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E217" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="F217" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="G217" s="30" t="s">
-        <v>1050</v>
-      </c>
-      <c r="H217" s="30" t="s">
-        <v>1051</v>
-      </c>
-      <c r="I217" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="J217" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="K217" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="L217" s="42">
-        <v>38880</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B218" s="6"/>
-      <c r="C218" s="29" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D218" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="E218" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="F218" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="G218" s="30" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H218" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="I218" s="31" t="s">
-        <v>1053</v>
-      </c>
-      <c r="J218" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="K218" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="L218" s="6"/>
-    </row>
-    <row r="219" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B219" s="6"/>
-      <c r="C219" s="29" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D219" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="E219" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="F219" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G219" s="30" t="s">
-        <v>1043</v>
-      </c>
-      <c r="H219" s="30" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I219" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="J219" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="K219" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="L219" s="6"/>
-    </row>
-    <row r="220" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B220" s="6"/>
-      <c r="C220" s="29" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D220" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="E220" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="F220" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G220" s="30" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H220" s="30" t="s">
-        <v>1058</v>
-      </c>
-      <c r="I220" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J220" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="K220" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="L220" s="6"/>
-    </row>
-    <row r="221" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="29" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B221" s="6"/>
-      <c r="C221" s="29" t="s">
-        <v>1060</v>
-      </c>
-      <c r="D221" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="E221" s="46" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F221" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="G221" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="H221" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="I221" s="31" t="s">
-        <v>1061</v>
-      </c>
-      <c r="J221" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="K221" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="L221" s="42">
-        <v>23200</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B222" s="6"/>
-      <c r="C222" s="29" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D222" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="E222" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="F222" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G222" s="30" t="s">
-        <v>1043</v>
-      </c>
-      <c r="H222" s="30" t="s">
-        <v>1063</v>
-      </c>
-      <c r="I222" s="31" t="s">
-        <v>1064</v>
-      </c>
-      <c r="J222" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="K222" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="L222" s="6"/>
-    </row>
-    <row r="223" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B223" s="6"/>
-      <c r="C223" s="29" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D223" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="E223" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="F223" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G223" s="30" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H223" s="30" t="s">
-        <v>1066</v>
-      </c>
-      <c r="I223" s="31" t="s">
-        <v>1067</v>
-      </c>
-      <c r="J223" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="K223" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="L223" s="6"/>
-    </row>
-    <row r="224" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B224" s="52" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C224" s="29" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D224" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="E224" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="F224" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="G224" s="30" t="s">
-        <v>1050</v>
-      </c>
-      <c r="H224" s="30" t="s">
-        <v>1051</v>
-      </c>
-      <c r="I224" s="31" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J224" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="K224" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="L224" s="42">
-        <v>29880</v>
-      </c>
-    </row>
-    <row r="225" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="47" t="s">
-        <v>987</v>
-      </c>
-      <c r="B225" s="48"/>
-      <c r="C225" s="47" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D225" s="49" t="s">
-        <v>381</v>
-      </c>
-      <c r="E225" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="F225" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="G225" s="49" t="s">
-        <v>1071</v>
-      </c>
-      <c r="H225" s="49" t="s">
-        <v>1072</v>
-      </c>
-      <c r="I225" s="50" t="s">
-        <v>1073</v>
-      </c>
-      <c r="J225" s="49" t="s">
-        <v>374</v>
-      </c>
-      <c r="K225" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="L225" s="48"/>
-    </row>
-    <row r="226" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B226" s="6"/>
-      <c r="C226" s="29" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D226" s="30" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E226" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F226" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="G226" s="30" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H226" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="I226" s="31" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J226" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="K226" s="46" t="s">
-        <v>1031</v>
-      </c>
-      <c r="L226" s="6"/>
-    </row>
-    <row r="227" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B227" s="6"/>
-      <c r="C227" s="29" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D227" s="30" t="s">
-        <v>454</v>
-      </c>
-      <c r="E227" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="F227" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="G227" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="H227" s="30" t="s">
-        <v>1079</v>
-      </c>
-      <c r="I227" s="31" t="s">
-        <v>1080</v>
-      </c>
-      <c r="J227" s="30" t="s">
-        <v>441</v>
-      </c>
-      <c r="K227" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="L227" s="6"/>
-    </row>
-    <row r="228" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B228" s="52" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C228" s="29" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D228" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="E228" s="30" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F228" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="G228" s="30" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H228" s="30" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I228" s="31" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J228" s="30" t="s">
-        <v>500</v>
-      </c>
-      <c r="K228" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="L228" s="42">
-        <v>45800</v>
-      </c>
-    </row>
-    <row r="229" spans="1:12" ht="65.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B229" s="6"/>
-      <c r="C229" s="29" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D229" s="30" t="s">
-        <v>474</v>
-      </c>
-      <c r="E229" s="30" t="s">
-        <v>631</v>
-      </c>
-      <c r="F229" s="30" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G229" s="30" t="s">
-        <v>1087</v>
-      </c>
-      <c r="H229" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="I229" s="31" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J229" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="K229" s="46" t="s">
-        <v>1031</v>
-      </c>
-      <c r="L229" s="42">
-        <v>13800</v>
-      </c>
-    </row>
-    <row r="230" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B230" s="6"/>
-      <c r="C230" s="29" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D230" s="30" t="s">
-        <v>540</v>
-      </c>
-      <c r="E230" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="F230" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="G230" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="H230" s="30" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I230" s="31" t="s">
-        <v>1091</v>
-      </c>
-      <c r="J230" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="K230" s="46" t="s">
-        <v>1031</v>
-      </c>
-      <c r="L230" s="42">
-        <v>15700</v>
-      </c>
-    </row>
-    <row r="231" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B231" s="6"/>
-      <c r="C231" s="29" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D231" s="30" t="s">
-        <v>561</v>
-      </c>
-      <c r="E231" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="F231" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="G231" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="H231" s="30" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I231" s="31" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J231" s="30" t="s">
-        <v>482</v>
-      </c>
-      <c r="K231" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="L231" s="42">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="232" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="29" t="s">
-        <v>987</v>
-      </c>
-      <c r="B232" s="6"/>
-      <c r="C232" s="29" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D232" s="30" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E232" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="F232" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G232" s="30" t="s">
-        <v>1097</v>
-      </c>
-      <c r="H232" s="30" t="s">
-        <v>1098</v>
-      </c>
-      <c r="I232" s="31" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J232" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="K232" s="46" t="s">
-        <v>446</v>
-      </c>
-      <c r="L232" s="6"/>
-    </row>
-    <row r="233" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="B233" s="48"/>
-      <c r="C233" s="47" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D233" s="49" t="s">
-        <v>570</v>
-      </c>
-      <c r="E233" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="F233" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="G233" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="H233" s="49" t="s">
-        <v>931</v>
-      </c>
-      <c r="I233" s="50" t="s">
-        <v>918</v>
-      </c>
-      <c r="J233" s="49" t="s">
-        <v>441</v>
-      </c>
-      <c r="K233" s="49" t="s">
-        <v>208</v>
-      </c>
-      <c r="L233" s="48"/>
-    </row>
-    <row r="234" spans="1:12" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B234" s="6"/>
-      <c r="C234" s="29" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D234" s="30" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E234" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="F234" s="30" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G234" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="H234" s="30" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I234" s="31" t="s">
-        <v>1105</v>
-      </c>
-      <c r="J234" s="30" t="s">
-        <v>1004</v>
-      </c>
-      <c r="K234" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="L234" s="42">
-        <v>29300</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
